--- a/VerveStacks_UZB_grids_kan15/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_UZB_grids_kan15/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_UZB_grids_kan15\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4340F09-EEBF-4AA8-9921-307E8B52E76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57292437-2A45-4437-9451-9B30154C7653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{84360B91-5514-48D2-B661-6955A371B510}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{4B6D9744-D306-4CFB-A81F-80E29C431A69}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -919,11 +919,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12435A95-68F4-48DB-AF1E-73C8F9471D41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{099C6D74-6E10-4C68-99F8-0E9912470A67}">
   <dimension ref="B3:S68"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -934,7 +934,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -978,7 +978,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>40.698678658589024</v>
       </c>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>40.225667574603349</v>
       </c>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>38.49046731123385</v>
       </c>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>39.709167100000009</v>
       </c>
     </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>38.273553949935753</v>
       </c>
     </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>41.068291911433192</v>
       </c>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>38.576495007818366</v>
       </c>
     </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>40.99834083796889</v>
       </c>
     </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -1347,7 +1347,7 @@
         <v>40.155603876595002</v>
       </c>
     </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>42.382481647963097</v>
       </c>
     </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>8</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>38.781919126074001</v>
       </c>
     </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>8</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>39.625780599999999</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>8</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>41.39254632589352</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>8</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>37.254153700000003</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>8</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>41.695259800000009</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>8</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>8</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>8</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>8</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>8</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>8</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
       <c r="O26" t="s">
         <v>89</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
       <c r="O27" t="s">
         <v>91</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
       <c r="O28" t="s">
         <v>93</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
       <c r="O29" t="s">
         <v>95</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
       <c r="O30" t="s">
         <v>97</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
       <c r="O31" t="s">
         <v>99</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
       <c r="O32" t="s">
         <v>101</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="33" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O33" t="s">
         <v>103</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="34" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O34" t="s">
         <v>105</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="35" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="35" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O35" t="s">
         <v>107</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="36" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O36" t="s">
         <v>109</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="37" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O37" t="s">
         <v>111</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="38" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O38" t="s">
         <v>113</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="39" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O39" t="s">
         <v>115</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="40" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O40" t="s">
         <v>117</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="41" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O41" t="s">
         <v>119</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="42" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O42" t="s">
         <v>121</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="43" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="43" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O43" t="s">
         <v>123</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="44" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O44" t="s">
         <v>125</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="45" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="45" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O45" t="s">
         <v>127</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="46" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O46" t="s">
         <v>129</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="47" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="47" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O47" t="s">
         <v>131</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="48" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O48" t="s">
         <v>133</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="49" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O49" t="s">
         <v>134</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="50" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O50" t="s">
         <v>135</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="51" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="51" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O51" t="s">
         <v>137</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="52" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="52" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O52" t="s">
         <v>139</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="53" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O53" t="s">
         <v>141</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="54" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O54" t="s">
         <v>142</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="55" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O55" t="s">
         <v>143</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="56" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="56" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O56" t="s">
         <v>145</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="57" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="57" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O57" t="s">
         <v>147</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="58" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="58" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O58" t="s">
         <v>149</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="59" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="59" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O59" t="s">
         <v>151</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="60" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="60" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O60" t="s">
         <v>153</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="61" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="61" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O61" t="s">
         <v>155</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="62" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="62" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O62" t="s">
         <v>157</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="63" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="63" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O63" t="s">
         <v>159</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="64" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="64" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O64" t="s">
         <v>161</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="65" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="65" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O65" t="s">
         <v>163</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="66" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="66" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O66" t="s">
         <v>165</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="67" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="67" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O67" t="s">
         <v>166</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="68" spans="15:19" x14ac:dyDescent="0.45">
+    <row r="68" spans="15:19" x14ac:dyDescent="0.25">
       <c r="O68" t="s">
         <v>168</v>
       </c>
